--- a/data/CZ_SK_U23_Six_Eight.xlsx
+++ b/data/CZ_SK_U23_Six_Eight.xlsx
@@ -497,7 +497,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Czech Republic + Slovakia  ·  59 candidates  ·  Progressive passing + defensive-actions volume  ·  Ranked by Six Score</t>
+          <t>Czech Republic + Slovakia (by nationality)  ·  59 candidates  ·  Progressive passing + defensive-actions volume  ·  Ranked by Six Score</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Czech Republic + Slovakia  ·  103 candidates  ·  Progressive passing, key passes, through passes, shot output  ·  Ranked by Eight Score</t>
+          <t>Czech Republic + Slovakia (by nationality)  ·  103 candidates  ·  Progressive passing, key passes, through passes, shot output  ·  Ranked by Eight Score</t>
         </is>
       </c>
     </row>

--- a/data/CZ_SK_U23_Six_Eight.xlsx
+++ b/data/CZ_SK_U23_Six_Eight.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Czech Republic + Slovakia (by nationality)  ·  Top 10 (senior first-team players only)  ·  Progressive passing + defensive-actions volume  ·  Ranked by Six Score</t>
+          <t>Czech + Slovak leagues (by league played in, any nationality)  ·  Top 15 (senior first-team players only)  ·  Progressive passing + defensive-actions volume  ·  Ranked by Six Score</t>
         </is>
       </c>
     </row>
@@ -723,17 +723,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>K. Karban</t>
+          <t>Y. Kambi</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Pohronie</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Czech II</t>
+          <t>Slovakia II</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -742,63 +742,61 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+          <t>Gambia</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v/>
       </c>
       <c r="H6" s="4" t="n">
-        <v>558</v>
+        <v>512</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>78.43000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.45</v>
+        <v>5.98</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>73.84</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.97</v>
+        <v>4.22</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.99</v>
+        <v>6.73</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.94</v>
+        <v>8.26</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>63.16</v>
+        <v>66.67</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>47.37</v>
+        <v>78.79000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>M. Szolgai</t>
+          <t>K. Karban</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Hungary II</t>
+          <t>Czech II</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -807,63 +805,63 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>2109</v>
+        <v>558</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>64.86</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>7.13</v>
+        <v>6.45</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>80.53</v>
+        <v>73.84</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>3.84</v>
+        <v>5.97</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>5.3</v>
+        <v>7.99</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>8.24</v>
+        <v>11.94</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>63.83</v>
+        <v>63.16</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>65.33</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>P. Švestka</t>
+          <t>C. Boah</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Petržalka Akadémia</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Czech II</t>
+          <t>Slovakia II</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -872,61 +870,63 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v/>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2249</v>
+        <v>462</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>57.77</v>
+        <v>67.8</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.89</v>
+        <v>7.79</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>86.14</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.43</v>
+        <v>4.29</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.65</v>
+        <v>6.88</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>61.39</v>
+        <v>50</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>53.42</v>
+        <v>56.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>A. Pesek</t>
+          <t>Miki García</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Inter Bratislava</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Czech II</t>
+          <t>Slovakia II</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -939,47 +939,49 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v/>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>2102</v>
+        <v>1231</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>56.89</v>
+        <v>58.35</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>6.98</v>
+        <v>5.85</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>85.33</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>3.55</v>
+        <v>4.31</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>5.21</v>
+        <v>6.1</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>8.01</v>
+        <v>11.84</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>66.43000000000001</v>
+        <v>63.04</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>33.33</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>S. Kop</t>
+          <t>P. Švestka</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -998,63 +1000,61 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="G10" s="4" t="n">
+        <v/>
       </c>
       <c r="H10" s="4" t="n">
-        <v>939</v>
+        <v>2249</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>56.4</v>
+        <v>57.77</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>77.87</v>
+        <v>86.14</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>5.15</v>
+        <v>4.43</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.9</v>
+        <v>5.65</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>9.24</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>69.64</v>
+        <v>61.39</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>48.15</v>
+        <v>53.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>D. Samek</t>
+          <t>F. Krawczyk</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Artis Brno</t>
+          <t>Stará Ľubovňa</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Czech II</t>
+          <t>Slovakia II</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1063,63 +1063,61 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v/>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1729</v>
+        <v>1789</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>51.1</v>
+        <v>57.45</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>5.23</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>80.13</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>2.93</v>
+        <v>5.89</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>3.97</v>
+        <v>7.85</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>7.84</v>
+        <v>11.67</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>64.44</v>
+        <v>58.05</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>53.33</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>T. Rigo</t>
+          <t>A. Pesek</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>England II</t>
+          <t>Czech II</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1132,108 +1130,427 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Slovakia, Czech Republic</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v/>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1861</v>
+        <v>2102</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>49.93</v>
+        <v>56.89</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.9</v>
+        <v>6.98</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>80.14</v>
+        <v>85.33</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.21</v>
+        <v>3.55</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.32</v>
+        <v>5.21</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>7.16</v>
+        <v>8.01</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>68.18000000000001</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>51.67</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>S. Kop</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Příbram</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Czech II</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>939</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>77.87</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>69.64</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>48.15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>D. Samek</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Artis Brno</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Czech II</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1729</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>64.44</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>53.33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>S. Mišík</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Považská Bystrica</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Slovakia II</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Senior First Team</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E15" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>838</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="n">
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="n">
         <v>47.74</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="K15" s="5" t="n">
         <v>3.87</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L15" s="5" t="n">
         <v>79.58</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>4.94</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>5.7</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>11.38</v>
       </c>
-      <c r="P13" s="5" t="n">
+      <c r="P15" s="5" t="n">
         <v>63.74</v>
       </c>
-      <c r="Q13" s="5" t="n">
+      <c r="Q15" s="5" t="n">
         <v>46.67</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Adam Yakubu</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>LNZ Cherkasy</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1422</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>88.04000000000001</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>71.19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Š. Černý</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Příbram</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Czech II</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1027</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>69.56999999999999</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>42.11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>D. Kastanek</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Czech II</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1478</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>82.67</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>73.03</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>41.18</v>
       </c>
     </row>
   </sheetData>
@@ -1251,7 +1568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1267,7 +1584,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Czech Republic + Slovakia (by nationality)  ·  Top 10 (youth academy + reserve/B-team players only)  ·  Progressive passing + defensive-actions volume  ·  Ranked by Six Score</t>
+          <t>Czech + Slovak leagues (by league played in, any nationality)  ·  Top 15 (youth academy + reserve/B-team players only)  ·  Progressive passing + defensive-actions volume  ·  Ranked by Six Score</t>
         </is>
       </c>
     </row>
@@ -2004,6 +2321,331 @@
       </c>
       <c r="Q13" s="5" t="n">
         <v>45.45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>L. Petr</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>MFK Karviná U17</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Czech U17</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Youth Academy</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>2103</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>69.04000000000001</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>82.67</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>70.66</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>47.62</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>M. Luzny</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Zbrojovka Brno U19</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Czech U19</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Youth Academy</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1638</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>O. Rittenauer</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Mladá Boleslav U19</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Czech U19</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Youth Academy</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>66.20999999999999</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>83.98</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>23.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>T. Škubala</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Baník Ostrava U19</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Czech U19</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Youth Academy</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1275</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>65.47</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>78.44</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>71.95999999999999</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>51.35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>V. Böhm</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Viktoria Plzeň U17</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Czech U17</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Youth Academy</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>591</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>81.84999999999999</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>67.61</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>44.44</v>
       </c>
     </row>
   </sheetData>
@@ -2021,7 +2663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2037,7 +2679,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Czech Republic + Slovakia (by nationality)  ·  Top 10 (senior first-team players only)  ·  Progressive passing, key passes, through passes, shot output  ·  Ranked by Eight Score</t>
+          <t>Czech + Slovak leagues (by league played in, any nationality)  ·  Top 15 (senior first-team players only)  ·  Progressive passing, key passes, through passes, shot output  ·  Ranked by Eight Score</t>
         </is>
       </c>
     </row>
@@ -2196,17 +2838,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>P. Vydra</t>
+          <t>D. Teah</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Czech</t>
+          <t>Czech II</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -2215,63 +2857,63 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1536</v>
+        <v>727</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>94.75</v>
+        <v>95.17</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>7.15</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>1.05</v>
+        <v>1.98</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>1</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>T. Jelínek</t>
+          <t>P. Vydra</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Czech II</t>
+          <t>Czech</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2280,61 +2922,63 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
-        <v/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1249</v>
+        <v>1536</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>94.29000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.07</v>
+        <v>7.15</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.15</v>
+        <v>0.76</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.66</v>
+        <v>1.05</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>2.67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>S. Varga</t>
+          <t>T. Jelínek</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Šamorín</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Slovakia II</t>
+          <t>Czech II</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2343,63 +2987,61 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Slovakia, Hungary</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v/>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1715</v>
+        <v>1249</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>94.02</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>6.66</v>
+        <v>8.07</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.68</v>
+        <v>1.15</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>1.26</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>L. Ambros</t>
+          <t>S. Varga</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Šamorín</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovakia II</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -2408,47 +3050,47 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Slovakia, Hungary</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1968</v>
+        <v>1715</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>89.69</v>
+        <v>94.02</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.85</v>
+        <v>6.66</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="9">
@@ -2519,17 +3161,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>M. Mateáš</t>
+          <t>F. Bzdyl</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Slovakia II</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2542,54 +3184,54 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>right</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2392</v>
+        <v>1047</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>85.73999999999999</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.36</v>
+        <v>7.56</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>J. Michlík</t>
+          <t>M. Mateáš</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Pohronie</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2603,7 +3245,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -2616,45 +3258,45 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1523</v>
+        <v>2392</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>85.69</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>4.08</v>
+        <v>6.36</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.47</v>
+        <v>0.34</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.59</v>
+        <v>0.34</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>3.01</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>M. Kušnír</t>
+          <t>J. Michlík</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Inter Bratislava</t>
+          <t>Pohronie</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2668,7 +3310,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
@@ -2681,50 +3323,50 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2301</v>
+        <v>1523</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>78.63</v>
+        <v>85.69</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.4</v>
+        <v>4.08</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.98</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>H. Hruska</t>
+          <t>M. Breznik</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Malženice</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Czech II</t>
+          <t>Slovakia II</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -2737,41 +3379,366 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>85.08</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>R. Štorman</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Karviná</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Czech</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1707</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>83.51000000000001</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Andrei</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Slovakia II</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Romania, Italy</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>768</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>83.29000000000001</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>M. Kušnír</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Inter Bratislava</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Slovakia II</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2301</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>78.63</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>H. Hruska</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Vlašim</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Czech II</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v/>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>1417</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="n">
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
         <v>78.37</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="K17" s="5" t="n">
         <v>6.16</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L17" s="5" t="n">
         <v>0.32</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>0.38</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>1.84</v>
       </c>
-      <c r="O13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="5" t="n">
+      <c r="O17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q13" s="5" t="n">
+      <c r="Q17" s="5" t="n">
         <v>1.91</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>X. Adang</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Senior First Team</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>2079</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -2789,7 +3756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2805,7 +3772,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Czech Republic + Slovakia (by nationality)  ·  Top 10 (youth academy + reserve/B-team players only)  ·  Progressive passing, key passes, through passes, shot output  ·  Ranked by Eight Score</t>
+          <t>Czech + Slovak leagues (by league played in, any nationality)  ·  Top 15 (youth academy + reserve/B-team players only)  ·  Progressive passing, key passes, through passes, shot output  ·  Ranked by Eight Score</t>
         </is>
       </c>
     </row>
@@ -3092,11 +4059,13 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>F. Rajcan</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v/>
+          <t>R. Filip</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Baník Ostrava U19</t>
+        </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -3155,13 +4124,11 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>R. Filip</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Baník Ostrava U19</t>
-        </is>
+          <t>F. Rajcan</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v/>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -3538,6 +4505,329 @@
       </c>
       <c r="Q13" s="5" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>R. Petruška</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Žilina II</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Slovakia II</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Reserve / B Team</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1901</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>94.39</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>F. Rada</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Viktoria Plzeň U17</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Czech U17</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Youth Academy</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>719</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>93.87</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>P. Lubor</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Slovan Liberec U19</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Czech U17</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Youth Academy</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1010</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>92.19</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Š. Sedlák</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Vysočina Jihlava U19</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Czech U19</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Youth Academy</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>615</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>91.92</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>V. Kotisek</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sparta Praha U19</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Czech U19</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Youth Academy</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1178</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>1.99</v>
       </c>
     </row>
   </sheetData>
